--- a/data/sample_dars.xlsx
+++ b/data/sample_dars.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I364"/>
+  <dimension ref="A1:I394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="C81" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="C83" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="C87" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="C90" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="C93" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C95" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C98" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="C102" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C105" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="C117" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="C127" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="C136" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="C137" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="C139" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="C140" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="C141" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="C142" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="C143" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="C144" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="C145" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="C146" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="C147" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="C149" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="C150" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="C151" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="C152" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="C153" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="C154" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="C155" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="C156" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="C157" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="C158" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="C159" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         </is>
       </c>
       <c r="C160" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="C161" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="C162" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="C163" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="C164" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="C165" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="C166" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="C167" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="C168" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="C169" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="C171" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="C175" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="C176" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="C177" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="C181" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="C183" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="C184" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="C185" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="C186" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="C187" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="C188" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="C189" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="C190" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="C191" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="C192" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="C193" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="C194" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="C195" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="C196" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="C197" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         </is>
       </c>
       <c r="C198" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="C199" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="C200" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="C201" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="C202" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="C203" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="C204" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="C205" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="C206" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="C207" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="C208" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="C209" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="C210" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="C211" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C212" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="C213" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="C215" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="C216" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="C217" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="C218" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="C219" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="C220" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="C221" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="C222" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="C223" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="C224" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="C225" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="C226" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="C227" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="C228" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="C229" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="C230" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="C231" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="C232" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="C233" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="C234" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="C235" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="C236" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="C237" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="C238" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="C239" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="C240" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="C241" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="C242" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="C243" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="C244" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="C245" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="C246" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="C247" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="C248" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="C249" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         </is>
       </c>
       <c r="C250" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="C251" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="C252" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="C253" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         </is>
       </c>
       <c r="C254" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="C255" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         </is>
       </c>
       <c r="C256" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="C257" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="C258" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="C259" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="C260" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="C261" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="C262" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="C263" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         </is>
       </c>
       <c r="C264" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         </is>
       </c>
       <c r="C265" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="C266" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="C267" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         </is>
       </c>
       <c r="C268" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="C269" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="C270" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="C271" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="C272" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="C273" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="C274" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="C275" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="C276" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="C277" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="C278" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="C279" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="C280" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="C281" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="C282" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="C283" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         </is>
       </c>
       <c r="C284" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="C285" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="C287" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="C288" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         </is>
       </c>
       <c r="C289" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         </is>
       </c>
       <c r="C290" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         </is>
       </c>
       <c r="C291" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="C292" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="C293" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="C294" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         </is>
       </c>
       <c r="C295" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="C296" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="C297" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="C298" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="C299" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         </is>
       </c>
       <c r="C300" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="C301" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="C302" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="C303" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="C304" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="C305" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         </is>
       </c>
       <c r="C306" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="C307" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="C308" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="C309" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="C310" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="C311" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="C312" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="C313" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         </is>
       </c>
       <c r="C314" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="C316" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="C317" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         </is>
       </c>
       <c r="C318" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="C319" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="C320" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="C321" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="C322" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="C323" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         </is>
       </c>
       <c r="C324" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="C325" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="C326" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         </is>
       </c>
       <c r="C327" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="C328" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         </is>
       </c>
       <c r="C329" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="C330" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="C331" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="C332" s="3" t="n">
-        <v>46280.25</v>
+        <v>46281.25</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="C333" s="3" t="n">
-        <v>46281.25</v>
+        <v>46282.25</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="C334" s="3" t="n">
-        <v>46282.25</v>
+        <v>46283.25</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="C335" s="3" t="n">
-        <v>46283.25</v>
+        <v>46284.25</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         </is>
       </c>
       <c r="C336" s="3" t="n">
-        <v>46284.25</v>
+        <v>46285.25</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="C337" s="3" t="n">
-        <v>46285.25</v>
+        <v>46286.25</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         </is>
       </c>
       <c r="C338" s="3" t="n">
-        <v>46286.25</v>
+        <v>46287.25</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="C339" s="3" t="n">
-        <v>46287.25</v>
+        <v>46288.25</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         </is>
       </c>
       <c r="C340" s="3" t="n">
-        <v>46288.25</v>
+        <v>46289.25</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         </is>
       </c>
       <c r="C341" s="3" t="n">
-        <v>46289.25</v>
+        <v>46290.25</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         </is>
       </c>
       <c r="C342" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.25</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>46291.25</v>
+        <v>46292.25</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         </is>
       </c>
       <c r="C344" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.25</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         </is>
       </c>
       <c r="C345" s="3" t="n">
-        <v>46293.25</v>
+        <v>46294.25</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         </is>
       </c>
       <c r="C346" s="3" t="n">
-        <v>46294.25</v>
+        <v>46295.25</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         </is>
       </c>
       <c r="C347" s="3" t="n">
-        <v>46295.25</v>
+        <v>46296.25</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         </is>
       </c>
       <c r="C348" s="3" t="n">
-        <v>46296.25</v>
+        <v>46297.25</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="C349" s="3" t="n">
-        <v>46297.25</v>
+        <v>46298.25</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         </is>
       </c>
       <c r="C350" s="3" t="n">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="C351" s="3" t="n">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C352" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.25</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>46301.25</v>
+        <v>46302.25</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="C354" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="C355" s="3" t="n">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="C356" s="3" t="n">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.25</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         </is>
       </c>
       <c r="C358" s="3" t="n">
-        <v>46306.25</v>
+        <v>46307.25</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         </is>
       </c>
       <c r="C359" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="C360" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="C361" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         </is>
       </c>
       <c r="C362" s="3" t="n">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="C363" s="3" t="n">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="C364" s="3" t="n">
-        <v>46309.25</v>
+        <v>46310.25</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -13200,6 +13200,1056 @@
         <v>10.995</v>
       </c>
       <c r="I364" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="n">
+        <v>46281.25</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F365" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H365" t="n">
+        <v>7.598</v>
+      </c>
+      <c r="I365" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="n">
+        <v>46282.25</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F366" t="n">
+        <v>4</v>
+      </c>
+      <c r="G366" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H366" t="n">
+        <v>7.593</v>
+      </c>
+      <c r="I366" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C367" s="3" t="n">
+        <v>46283.25</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="F367" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H367" t="n">
+        <v>7.604</v>
+      </c>
+      <c r="I367" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C368" s="3" t="n">
+        <v>46284.25</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="F368" t="n">
+        <v>4</v>
+      </c>
+      <c r="G368" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H368" t="n">
+        <v>7.606</v>
+      </c>
+      <c r="I368" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C369" s="3" t="n">
+        <v>46285.25</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F369" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H369" t="n">
+        <v>7.595</v>
+      </c>
+      <c r="I369" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C370" s="3" t="n">
+        <v>46286.25</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="F370" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G370" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H370" t="n">
+        <v>7.596</v>
+      </c>
+      <c r="I370" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C371" s="3" t="n">
+        <v>46287.25</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="F371" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G371" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H371" t="n">
+        <v>7.607</v>
+      </c>
+      <c r="I371" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C372" s="3" t="n">
+        <v>46288.25</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>59.94</v>
+      </c>
+      <c r="F372" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H372" t="n">
+        <v>7.603</v>
+      </c>
+      <c r="I372" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="n">
+        <v>46289.25</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="F373" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H373" t="n">
+        <v>7.593</v>
+      </c>
+      <c r="I373" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C374" s="3" t="n">
+        <v>46290.25</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="F374" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G374" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H374" t="n">
+        <v>7.599</v>
+      </c>
+      <c r="I374" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C375" s="3" t="n">
+        <v>46291.25</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="F375" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G375" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H375" t="n">
+        <v>7.608</v>
+      </c>
+      <c r="I375" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C376" s="3" t="n">
+        <v>46292.25</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>60.07</v>
+      </c>
+      <c r="F376" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H376" t="n">
+        <v>7.599</v>
+      </c>
+      <c r="I376" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C377" s="3" t="n">
+        <v>46293.25</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="F377" t="n">
+        <v>4</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H377" t="n">
+        <v>7.593</v>
+      </c>
+      <c r="I377" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C378" s="3" t="n">
+        <v>46294.25</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="F378" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H378" t="n">
+        <v>7.603</v>
+      </c>
+      <c r="I378" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C379" s="3" t="n">
+        <v>46295.25</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>59.81</v>
+      </c>
+      <c r="F379" t="n">
+        <v>4</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H379" t="n">
+        <v>7.607</v>
+      </c>
+      <c r="I379" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C380" s="3" t="n">
+        <v>46296.25</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="F380" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G380" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H380" t="n">
+        <v>7.595</v>
+      </c>
+      <c r="I380" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C381" s="3" t="n">
+        <v>46297.25</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="F381" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H381" t="n">
+        <v>7.595</v>
+      </c>
+      <c r="I381" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C382" s="3" t="n">
+        <v>46298.25</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="F382" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H382" t="n">
+        <v>7.606</v>
+      </c>
+      <c r="I382" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C383" s="3" t="n">
+        <v>46299.25</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="F383" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H383" t="n">
+        <v>7.604</v>
+      </c>
+      <c r="I383" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C384" s="3" t="n">
+        <v>46300.25</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="F384" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G384" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H384" t="n">
+        <v>7.593</v>
+      </c>
+      <c r="I384" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C385" s="3" t="n">
+        <v>46301.25</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="F385" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H385" t="n">
+        <v>7.598</v>
+      </c>
+      <c r="I385" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C386" s="3" t="n">
+        <v>46302.25</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="F386" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H386" t="n">
+        <v>7.608</v>
+      </c>
+      <c r="I386" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C387" s="3" t="n">
+        <v>46303.25</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="F387" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H387" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I387" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="n">
+        <v>46304.25</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="F388" t="n">
+        <v>4</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H388" t="n">
+        <v>7.592</v>
+      </c>
+      <c r="I388" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C389" s="3" t="n">
+        <v>46305.25</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="F389" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="G389" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H389" t="n">
+        <v>7.602</v>
+      </c>
+      <c r="I389" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C390" s="3" t="n">
+        <v>46306.25</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="F390" t="n">
+        <v>4</v>
+      </c>
+      <c r="G390" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H390" t="n">
+        <v>7.607</v>
+      </c>
+      <c r="I390" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C391" s="3" t="n">
+        <v>46307.25</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="F391" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G391" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H391" t="n">
+        <v>7.596</v>
+      </c>
+      <c r="I391" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C392" s="3" t="n">
+        <v>46308.25</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="F392" t="n">
+        <v>4</v>
+      </c>
+      <c r="G392" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H392" t="n">
+        <v>7.594</v>
+      </c>
+      <c r="I392" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C393" s="3" t="n">
+        <v>46309.25</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>59.81</v>
+      </c>
+      <c r="F393" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="G393" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H393" t="n">
+        <v>7.605</v>
+      </c>
+      <c r="I393" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>DEMO-014</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Восточное</t>
+        </is>
+      </c>
+      <c r="C394" s="3" t="n">
+        <v>46310.25</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="F394" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G394" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H394" t="n">
+        <v>7.605</v>
+      </c>
+      <c r="I394" t="n">
         <v>12</v>
       </c>
     </row>

--- a/data/sample_dars.xlsx
+++ b/data/sample_dars.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I394"/>
+  <dimension ref="A1:J394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,7 @@
     <col width="29" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -497,6 +498,11 @@
           <t>Начальная толщина стенки, мм</t>
         </is>
       </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Дебит жидкости, м³/сут</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -532,6 +538,9 @@
       <c r="I2" t="n">
         <v>12</v>
       </c>
+      <c r="J2" t="n">
+        <v>44.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -567,6 +576,9 @@
       <c r="I3" t="n">
         <v>12</v>
       </c>
+      <c r="J3" t="n">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -602,6 +614,9 @@
       <c r="I4" t="n">
         <v>12</v>
       </c>
+      <c r="J4" t="n">
+        <v>45.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -637,6 +652,9 @@
       <c r="I5" t="n">
         <v>12</v>
       </c>
+      <c r="J5" t="n">
+        <v>45.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -672,6 +690,9 @@
       <c r="I6" t="n">
         <v>12</v>
       </c>
+      <c r="J6" t="n">
+        <v>44.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -707,6 +728,9 @@
       <c r="I7" t="n">
         <v>12</v>
       </c>
+      <c r="J7" t="n">
+        <v>44.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -742,6 +766,9 @@
       <c r="I8" t="n">
         <v>12</v>
       </c>
+      <c r="J8" t="n">
+        <v>45.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -777,6 +804,9 @@
       <c r="I9" t="n">
         <v>12</v>
       </c>
+      <c r="J9" t="n">
+        <v>44.8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -812,6 +842,9 @@
       <c r="I10" t="n">
         <v>12</v>
       </c>
+      <c r="J10" t="n">
+        <v>44.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -847,6 +880,9 @@
       <c r="I11" t="n">
         <v>12</v>
       </c>
+      <c r="J11" t="n">
+        <v>45.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -882,6 +918,9 @@
       <c r="I12" t="n">
         <v>12</v>
       </c>
+      <c r="J12" t="n">
+        <v>45.8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -917,6 +956,9 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
+      <c r="J13" t="n">
+        <v>44.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -952,6 +994,9 @@
       <c r="I14" t="n">
         <v>12</v>
       </c>
+      <c r="J14" t="n">
+        <v>44.4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -987,6 +1032,9 @@
       <c r="I15" t="n">
         <v>12</v>
       </c>
+      <c r="J15" t="n">
+        <v>45.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1022,6 +1070,9 @@
       <c r="I16" t="n">
         <v>12</v>
       </c>
+      <c r="J16" t="n">
+        <v>45.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1057,6 +1108,9 @@
       <c r="I17" t="n">
         <v>12</v>
       </c>
+      <c r="J17" t="n">
+        <v>44.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1092,6 +1146,9 @@
       <c r="I18" t="n">
         <v>12</v>
       </c>
+      <c r="J18" t="n">
+        <v>44.8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1127,6 +1184,9 @@
       <c r="I19" t="n">
         <v>12</v>
       </c>
+      <c r="J19" t="n">
+        <v>45.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1162,6 +1222,9 @@
       <c r="I20" t="n">
         <v>12</v>
       </c>
+      <c r="J20" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1197,6 +1260,9 @@
       <c r="I21" t="n">
         <v>12</v>
       </c>
+      <c r="J21" t="n">
+        <v>44.1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1232,6 +1298,9 @@
       <c r="I22" t="n">
         <v>12</v>
       </c>
+      <c r="J22" t="n">
+        <v>45.3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1267,6 +1336,9 @@
       <c r="I23" t="n">
         <v>12</v>
       </c>
+      <c r="J23" t="n">
+        <v>45.8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1302,6 +1374,9 @@
       <c r="I24" t="n">
         <v>12</v>
       </c>
+      <c r="J24" t="n">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1337,6 +1412,9 @@
       <c r="I25" t="n">
         <v>12</v>
       </c>
+      <c r="J25" t="n">
+        <v>44.3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1372,6 +1450,9 @@
       <c r="I26" t="n">
         <v>12</v>
       </c>
+      <c r="J26" t="n">
+        <v>45.7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1407,6 +1488,9 @@
       <c r="I27" t="n">
         <v>12</v>
       </c>
+      <c r="J27" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1442,6 +1526,9 @@
       <c r="I28" t="n">
         <v>12</v>
       </c>
+      <c r="J28" t="n">
+        <v>44.2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1477,6 +1564,9 @@
       <c r="I29" t="n">
         <v>12</v>
       </c>
+      <c r="J29" t="n">
+        <v>44.7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1512,6 +1602,9 @@
       <c r="I30" t="n">
         <v>12</v>
       </c>
+      <c r="J30" t="n">
+        <v>45.9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1547,6 +1640,9 @@
       <c r="I31" t="n">
         <v>12</v>
       </c>
+      <c r="J31" t="n">
+        <v>45.1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1582,6 +1678,9 @@
       <c r="I32" t="n">
         <v>12</v>
       </c>
+      <c r="J32" t="n">
+        <v>60.8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1617,6 +1716,9 @@
       <c r="I33" t="n">
         <v>12</v>
       </c>
+      <c r="J33" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1652,6 +1754,9 @@
       <c r="I34" t="n">
         <v>12</v>
       </c>
+      <c r="J34" t="n">
+        <v>63.1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1687,6 +1792,9 @@
       <c r="I35" t="n">
         <v>12</v>
       </c>
+      <c r="J35" t="n">
+        <v>61.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1722,6 +1830,9 @@
       <c r="I36" t="n">
         <v>12</v>
       </c>
+      <c r="J36" t="n">
+        <v>61.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1757,6 +1868,9 @@
       <c r="I37" t="n">
         <v>12</v>
       </c>
+      <c r="J37" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1792,6 +1906,9 @@
       <c r="I38" t="n">
         <v>12</v>
       </c>
+      <c r="J38" t="n">
+        <v>62.6</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1827,6 +1944,9 @@
       <c r="I39" t="n">
         <v>12</v>
       </c>
+      <c r="J39" t="n">
+        <v>60.8</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1862,6 +1982,9 @@
       <c r="I40" t="n">
         <v>12</v>
       </c>
+      <c r="J40" t="n">
+        <v>61.7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1897,6 +2020,9 @@
       <c r="I41" t="n">
         <v>12</v>
       </c>
+      <c r="J41" t="n">
+        <v>63.2</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1932,6 +2058,9 @@
       <c r="I42" t="n">
         <v>12</v>
       </c>
+      <c r="J42" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1967,6 +2096,9 @@
       <c r="I43" t="n">
         <v>12</v>
       </c>
+      <c r="J43" t="n">
+        <v>60.8</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2002,6 +2134,9 @@
       <c r="I44" t="n">
         <v>12</v>
       </c>
+      <c r="J44" t="n">
+        <v>62.3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2037,6 +2172,9 @@
       <c r="I45" t="n">
         <v>12</v>
       </c>
+      <c r="J45" t="n">
+        <v>63.1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2072,6 +2210,9 @@
       <c r="I46" t="n">
         <v>12</v>
       </c>
+      <c r="J46" t="n">
+        <v>61.4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,6 +2248,9 @@
       <c r="I47" t="n">
         <v>12</v>
       </c>
+      <c r="J47" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2142,6 +2286,9 @@
       <c r="I48" t="n">
         <v>12</v>
       </c>
+      <c r="J48" t="n">
+        <v>62.9</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2177,6 +2324,9 @@
       <c r="I49" t="n">
         <v>12</v>
       </c>
+      <c r="J49" t="n">
+        <v>62.8</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2212,6 +2362,9 @@
       <c r="I50" t="n">
         <v>12</v>
       </c>
+      <c r="J50" t="n">
+        <v>60.9</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2247,6 +2400,9 @@
       <c r="I51" t="n">
         <v>12</v>
       </c>
+      <c r="J51" t="n">
+        <v>61.5</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2282,6 +2438,9 @@
       <c r="I52" t="n">
         <v>12</v>
       </c>
+      <c r="J52" t="n">
+        <v>63.2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2317,6 +2476,9 @@
       <c r="I53" t="n">
         <v>12</v>
       </c>
+      <c r="J53" t="n">
+        <v>62.2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2352,6 +2514,9 @@
       <c r="I54" t="n">
         <v>12</v>
       </c>
+      <c r="J54" t="n">
+        <v>60.8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2387,6 +2552,9 @@
       <c r="I55" t="n">
         <v>12</v>
       </c>
+      <c r="J55" t="n">
+        <v>62.1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2422,6 +2590,9 @@
       <c r="I56" t="n">
         <v>12</v>
       </c>
+      <c r="J56" t="n">
+        <v>63.2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2457,6 +2628,9 @@
       <c r="I57" t="n">
         <v>12</v>
       </c>
+      <c r="J57" t="n">
+        <v>61.5</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2492,6 +2666,9 @@
       <c r="I58" t="n">
         <v>12</v>
       </c>
+      <c r="J58" t="n">
+        <v>60.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2527,6 +2704,9 @@
       <c r="I59" t="n">
         <v>12</v>
       </c>
+      <c r="J59" t="n">
+        <v>62.7</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2562,6 +2742,9 @@
       <c r="I60" t="n">
         <v>12</v>
       </c>
+      <c r="J60" t="n">
+        <v>62.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2597,6 +2780,9 @@
       <c r="I61" t="n">
         <v>12</v>
       </c>
+      <c r="J61" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2632,6 +2818,9 @@
       <c r="I62" t="n">
         <v>12</v>
       </c>
+      <c r="J62" t="n">
+        <v>37.8</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2667,6 +2856,9 @@
       <c r="I63" t="n">
         <v>12</v>
       </c>
+      <c r="J63" t="n">
+        <v>38.8</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2702,6 +2894,9 @@
       <c r="I64" t="n">
         <v>12</v>
       </c>
+      <c r="J64" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2737,6 +2932,9 @@
       <c r="I65" t="n">
         <v>12</v>
       </c>
+      <c r="J65" t="n">
+        <v>37.2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2772,6 +2970,9 @@
       <c r="I66" t="n">
         <v>12</v>
       </c>
+      <c r="J66" t="n">
+        <v>38.2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2807,6 +3008,9 @@
       <c r="I67" t="n">
         <v>12</v>
       </c>
+      <c r="J67" t="n">
+        <v>38.7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2842,6 +3046,9 @@
       <c r="I68" t="n">
         <v>12</v>
       </c>
+      <c r="J68" t="n">
+        <v>37.6</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2877,6 +3084,9 @@
       <c r="I69" t="n">
         <v>12</v>
       </c>
+      <c r="J69" t="n">
+        <v>37.4</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2912,6 +3122,9 @@
       <c r="I70" t="n">
         <v>12</v>
       </c>
+      <c r="J70" t="n">
+        <v>38.5</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2947,6 +3160,9 @@
       <c r="I71" t="n">
         <v>12</v>
       </c>
+      <c r="J71" t="n">
+        <v>38.5</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2982,6 +3198,9 @@
       <c r="I72" t="n">
         <v>12</v>
       </c>
+      <c r="J72" t="n">
+        <v>37.4</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3017,6 +3236,9 @@
       <c r="I73" t="n">
         <v>12</v>
       </c>
+      <c r="J73" t="n">
+        <v>37.7</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3052,6 +3274,9 @@
       <c r="I74" t="n">
         <v>12</v>
       </c>
+      <c r="J74" t="n">
+        <v>38.7</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3087,6 +3312,9 @@
       <c r="I75" t="n">
         <v>12</v>
       </c>
+      <c r="J75" t="n">
+        <v>38.1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3122,6 +3350,9 @@
       <c r="I76" t="n">
         <v>12</v>
       </c>
+      <c r="J76" t="n">
+        <v>37.2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3157,6 +3388,9 @@
       <c r="I77" t="n">
         <v>12</v>
       </c>
+      <c r="J77" t="n">
+        <v>38.1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3192,6 +3426,9 @@
       <c r="I78" t="n">
         <v>12</v>
       </c>
+      <c r="J78" t="n">
+        <v>38.7</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3227,6 +3464,9 @@
       <c r="I79" t="n">
         <v>12</v>
       </c>
+      <c r="J79" t="n">
+        <v>37.7</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3262,6 +3502,9 @@
       <c r="I80" t="n">
         <v>12</v>
       </c>
+      <c r="J80" t="n">
+        <v>37.3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3297,6 +3540,9 @@
       <c r="I81" t="n">
         <v>12</v>
       </c>
+      <c r="J81" t="n">
+        <v>38.4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3332,6 +3578,9 @@
       <c r="I82" t="n">
         <v>12</v>
       </c>
+      <c r="J82" t="n">
+        <v>38.6</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3367,6 +3616,9 @@
       <c r="I83" t="n">
         <v>12</v>
       </c>
+      <c r="J83" t="n">
+        <v>37.4</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3402,6 +3654,9 @@
       <c r="I84" t="n">
         <v>12</v>
       </c>
+      <c r="J84" t="n">
+        <v>37.6</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3437,6 +3692,9 @@
       <c r="I85" t="n">
         <v>12</v>
       </c>
+      <c r="J85" t="n">
+        <v>38.7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3472,6 +3730,9 @@
       <c r="I86" t="n">
         <v>12</v>
       </c>
+      <c r="J86" t="n">
+        <v>38.2</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3507,6 +3768,9 @@
       <c r="I87" t="n">
         <v>12</v>
       </c>
+      <c r="J87" t="n">
+        <v>37.3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3542,6 +3806,9 @@
       <c r="I88" t="n">
         <v>12</v>
       </c>
+      <c r="J88" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3577,6 +3844,9 @@
       <c r="I89" t="n">
         <v>12</v>
       </c>
+      <c r="J89" t="n">
+        <v>38.8</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3612,6 +3882,9 @@
       <c r="I90" t="n">
         <v>12</v>
       </c>
+      <c r="J90" t="n">
+        <v>37.9</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3647,6 +3920,9 @@
       <c r="I91" t="n">
         <v>12</v>
       </c>
+      <c r="J91" t="n">
+        <v>37.3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3682,6 +3958,9 @@
       <c r="I92" t="n">
         <v>12</v>
       </c>
+      <c r="J92" t="n">
+        <v>81.09999999999999</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3717,6 +3996,9 @@
       <c r="I93" t="n">
         <v>12</v>
       </c>
+      <c r="J93" t="n">
+        <v>81.09999999999999</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3752,6 +4034,9 @@
       <c r="I94" t="n">
         <v>12</v>
       </c>
+      <c r="J94" t="n">
+        <v>78.7</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3787,6 +4072,9 @@
       <c r="I95" t="n">
         <v>12</v>
       </c>
+      <c r="J95" t="n">
+        <v>79.3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3822,6 +4110,9 @@
       <c r="I96" t="n">
         <v>12</v>
       </c>
+      <c r="J96" t="n">
+        <v>81.5</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3857,6 +4148,9 @@
       <c r="I97" t="n">
         <v>12</v>
       </c>
+      <c r="J97" t="n">
+        <v>80.3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3892,6 +4186,9 @@
       <c r="I98" t="n">
         <v>12</v>
       </c>
+      <c r="J98" t="n">
+        <v>78.40000000000001</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3927,6 +4224,9 @@
       <c r="I99" t="n">
         <v>12</v>
       </c>
+      <c r="J99" t="n">
+        <v>80.09999999999999</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3962,6 +4262,9 @@
       <c r="I100" t="n">
         <v>12</v>
       </c>
+      <c r="J100" t="n">
+        <v>81.59999999999999</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3997,6 +4300,9 @@
       <c r="I101" t="n">
         <v>12</v>
       </c>
+      <c r="J101" t="n">
+        <v>79.5</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4032,6 +4338,9 @@
       <c r="I102" t="n">
         <v>12</v>
       </c>
+      <c r="J102" t="n">
+        <v>78.59999999999999</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4067,6 +4376,9 @@
       <c r="I103" t="n">
         <v>12</v>
       </c>
+      <c r="J103" t="n">
+        <v>80.90000000000001</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4102,6 +4414,9 @@
       <c r="I104" t="n">
         <v>12</v>
       </c>
+      <c r="J104" t="n">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4137,6 +4452,9 @@
       <c r="I105" t="n">
         <v>12</v>
       </c>
+      <c r="J105" t="n">
+        <v>78.8</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4172,6 +4490,9 @@
       <c r="I106" t="n">
         <v>12</v>
       </c>
+      <c r="J106" t="n">
+        <v>79.09999999999999</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4207,6 +4528,9 @@
       <c r="I107" t="n">
         <v>12</v>
       </c>
+      <c r="J107" t="n">
+        <v>81.40000000000001</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4242,6 +4566,9 @@
       <c r="I108" t="n">
         <v>12</v>
       </c>
+      <c r="J108" t="n">
+        <v>80.59999999999999</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4277,6 +4604,9 @@
       <c r="I109" t="n">
         <v>12</v>
       </c>
+      <c r="J109" t="n">
+        <v>78.40000000000001</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4312,6 +4642,9 @@
       <c r="I110" t="n">
         <v>12</v>
       </c>
+      <c r="J110" t="n">
+        <v>79.8</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4347,6 +4680,9 @@
       <c r="I111" t="n">
         <v>12</v>
       </c>
+      <c r="J111" t="n">
+        <v>81.59999999999999</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4382,6 +4718,9 @@
       <c r="I112" t="n">
         <v>12</v>
       </c>
+      <c r="J112" t="n">
+        <v>79.7</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4417,6 +4756,9 @@
       <c r="I113" t="n">
         <v>12</v>
       </c>
+      <c r="J113" t="n">
+        <v>78.5</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4452,6 +4794,9 @@
       <c r="I114" t="n">
         <v>12</v>
       </c>
+      <c r="J114" t="n">
+        <v>80.59999999999999</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4487,6 +4832,9 @@
       <c r="I115" t="n">
         <v>12</v>
       </c>
+      <c r="J115" t="n">
+        <v>81.40000000000001</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4522,6 +4870,9 @@
       <c r="I116" t="n">
         <v>12</v>
       </c>
+      <c r="J116" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4557,6 +4908,9 @@
       <c r="I117" t="n">
         <v>12</v>
       </c>
+      <c r="J117" t="n">
+        <v>78.90000000000001</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4592,6 +4946,9 @@
       <c r="I118" t="n">
         <v>12</v>
       </c>
+      <c r="J118" t="n">
+        <v>81.3</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4627,6 +4984,9 @@
       <c r="I119" t="n">
         <v>12</v>
       </c>
+      <c r="J119" t="n">
+        <v>80.8</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4662,6 +5022,9 @@
       <c r="I120" t="n">
         <v>12</v>
       </c>
+      <c r="J120" t="n">
+        <v>78.5</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4697,6 +5060,9 @@
       <c r="I121" t="n">
         <v>12</v>
       </c>
+      <c r="J121" t="n">
+        <v>79.59999999999999</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4732,6 +5098,9 @@
       <c r="I122" t="n">
         <v>12</v>
       </c>
+      <c r="J122" t="n">
+        <v>122.4</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4767,6 +5136,9 @@
       <c r="I123" t="n">
         <v>12</v>
       </c>
+      <c r="J123" t="n">
+        <v>119.3</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4802,6 +5174,9 @@
       <c r="I124" t="n">
         <v>12</v>
       </c>
+      <c r="J124" t="n">
+        <v>117.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4837,6 +5212,9 @@
       <c r="I125" t="n">
         <v>12</v>
       </c>
+      <c r="J125" t="n">
+        <v>121.2</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4872,6 +5250,9 @@
       <c r="I126" t="n">
         <v>12</v>
       </c>
+      <c r="J126" t="n">
+        <v>121.9</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4907,6 +5288,9 @@
       <c r="I127" t="n">
         <v>12</v>
       </c>
+      <c r="J127" t="n">
+        <v>118.3</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4942,6 +5326,9 @@
       <c r="I128" t="n">
         <v>12</v>
       </c>
+      <c r="J128" t="n">
+        <v>118.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4977,6 +5364,9 @@
       <c r="I129" t="n">
         <v>12</v>
       </c>
+      <c r="J129" t="n">
+        <v>122.1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5012,6 +5402,9 @@
       <c r="I130" t="n">
         <v>12</v>
       </c>
+      <c r="J130" t="n">
+        <v>120.9</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5047,6 +5440,9 @@
       <c r="I131" t="n">
         <v>12</v>
       </c>
+      <c r="J131" t="n">
+        <v>117.7</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5082,6 +5478,9 @@
       <c r="I132" t="n">
         <v>12</v>
       </c>
+      <c r="J132" t="n">
+        <v>119.7</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5117,6 +5516,9 @@
       <c r="I133" t="n">
         <v>12</v>
       </c>
+      <c r="J133" t="n">
+        <v>122.4</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5152,6 +5554,9 @@
       <c r="I134" t="n">
         <v>12</v>
       </c>
+      <c r="J134" t="n">
+        <v>119.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5187,6 +5592,9 @@
       <c r="I135" t="n">
         <v>12</v>
       </c>
+      <c r="J135" t="n">
+        <v>117.7</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5222,6 +5630,9 @@
       <c r="I136" t="n">
         <v>12</v>
       </c>
+      <c r="J136" t="n">
+        <v>120.9</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5257,6 +5668,9 @@
       <c r="I137" t="n">
         <v>12</v>
       </c>
+      <c r="J137" t="n">
+        <v>122.1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5292,6 +5706,9 @@
       <c r="I138" t="n">
         <v>12</v>
       </c>
+      <c r="J138" t="n">
+        <v>118.6</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5327,6 +5744,9 @@
       <c r="I139" t="n">
         <v>12</v>
       </c>
+      <c r="J139" t="n">
+        <v>118.3</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5362,6 +5782,9 @@
       <c r="I140" t="n">
         <v>12</v>
       </c>
+      <c r="J140" t="n">
+        <v>121.9</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5397,6 +5820,9 @@
       <c r="I141" t="n">
         <v>12</v>
       </c>
+      <c r="J141" t="n">
+        <v>121.2</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5432,6 +5858,9 @@
       <c r="I142" t="n">
         <v>12</v>
       </c>
+      <c r="J142" t="n">
+        <v>117.8</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5467,6 +5896,9 @@
       <c r="I143" t="n">
         <v>12</v>
       </c>
+      <c r="J143" t="n">
+        <v>119.3</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5502,6 +5934,9 @@
       <c r="I144" t="n">
         <v>12</v>
       </c>
+      <c r="J144" t="n">
+        <v>122.4</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5537,6 +5972,9 @@
       <c r="I145" t="n">
         <v>12</v>
       </c>
+      <c r="J145" t="n">
+        <v>120.1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5572,6 +6010,9 @@
       <c r="I146" t="n">
         <v>12</v>
       </c>
+      <c r="J146" t="n">
+        <v>117.6</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5607,6 +6048,9 @@
       <c r="I147" t="n">
         <v>12</v>
       </c>
+      <c r="J147" t="n">
+        <v>120.6</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5642,6 +6086,9 @@
       <c r="I148" t="n">
         <v>12</v>
       </c>
+      <c r="J148" t="n">
+        <v>122.2</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5677,6 +6124,9 @@
       <c r="I149" t="n">
         <v>12</v>
       </c>
+      <c r="J149" t="n">
+        <v>118.9</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5712,6 +6162,9 @@
       <c r="I150" t="n">
         <v>12</v>
       </c>
+      <c r="J150" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5747,6 +6200,9 @@
       <c r="I151" t="n">
         <v>12</v>
       </c>
+      <c r="J151" t="n">
+        <v>121.6</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5782,6 +6238,9 @@
       <c r="I152" t="n">
         <v>12</v>
       </c>
+      <c r="J152" t="n">
+        <v>25.2</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5817,6 +6276,9 @@
       <c r="I153" t="n">
         <v>12</v>
       </c>
+      <c r="J153" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5852,6 +6314,9 @@
       <c r="I154" t="n">
         <v>12</v>
       </c>
+      <c r="J154" t="n">
+        <v>24.9</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5887,6 +6352,9 @@
       <c r="I155" t="n">
         <v>12</v>
       </c>
+      <c r="J155" t="n">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5922,6 +6390,9 @@
       <c r="I156" t="n">
         <v>12</v>
       </c>
+      <c r="J156" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5957,6 +6428,9 @@
       <c r="I157" t="n">
         <v>12</v>
       </c>
+      <c r="J157" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5992,6 +6466,9 @@
       <c r="I158" t="n">
         <v>12</v>
       </c>
+      <c r="J158" t="n">
+        <v>25.2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6027,6 +6504,9 @@
       <c r="I159" t="n">
         <v>12</v>
       </c>
+      <c r="J159" t="n">
+        <v>25.4</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6062,6 +6542,9 @@
       <c r="I160" t="n">
         <v>12</v>
       </c>
+      <c r="J160" t="n">
+        <v>24.7</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6097,6 +6580,9 @@
       <c r="I161" t="n">
         <v>12</v>
       </c>
+      <c r="J161" t="n">
+        <v>24.6</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6132,6 +6618,9 @@
       <c r="I162" t="n">
         <v>12</v>
       </c>
+      <c r="J162" t="n">
+        <v>25.4</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6167,6 +6656,9 @@
       <c r="I163" t="n">
         <v>12</v>
       </c>
+      <c r="J163" t="n">
+        <v>25.3</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6202,6 +6694,9 @@
       <c r="I164" t="n">
         <v>12</v>
       </c>
+      <c r="J164" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6237,6 +6732,9 @@
       <c r="I165" t="n">
         <v>12</v>
       </c>
+      <c r="J165" t="n">
+        <v>24.8</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6272,6 +6770,9 @@
       <c r="I166" t="n">
         <v>12</v>
       </c>
+      <c r="J166" t="n">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6307,6 +6808,9 @@
       <c r="I167" t="n">
         <v>12</v>
       </c>
+      <c r="J167" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6342,6 +6846,9 @@
       <c r="I168" t="n">
         <v>12</v>
       </c>
+      <c r="J168" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6377,6 +6884,9 @@
       <c r="I169" t="n">
         <v>12</v>
       </c>
+      <c r="J169" t="n">
+        <v>25.1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6412,6 +6922,9 @@
       <c r="I170" t="n">
         <v>12</v>
       </c>
+      <c r="J170" t="n">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6447,6 +6960,9 @@
       <c r="I171" t="n">
         <v>12</v>
       </c>
+      <c r="J171" t="n">
+        <v>24.8</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6482,6 +6998,9 @@
       <c r="I172" t="n">
         <v>12</v>
       </c>
+      <c r="J172" t="n">
+        <v>24.6</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6517,6 +7036,9 @@
       <c r="I173" t="n">
         <v>12</v>
       </c>
+      <c r="J173" t="n">
+        <v>25.3</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6552,6 +7074,9 @@
       <c r="I174" t="n">
         <v>12</v>
       </c>
+      <c r="J174" t="n">
+        <v>25.3</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6587,6 +7112,9 @@
       <c r="I175" t="n">
         <v>12</v>
       </c>
+      <c r="J175" t="n">
+        <v>24.6</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6622,6 +7150,9 @@
       <c r="I176" t="n">
         <v>12</v>
       </c>
+      <c r="J176" t="n">
+        <v>24.8</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6657,6 +7188,9 @@
       <c r="I177" t="n">
         <v>12</v>
       </c>
+      <c r="J177" t="n">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6692,6 +7226,9 @@
       <c r="I178" t="n">
         <v>12</v>
       </c>
+      <c r="J178" t="n">
+        <v>25.1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6727,6 +7264,9 @@
       <c r="I179" t="n">
         <v>12</v>
       </c>
+      <c r="J179" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6762,6 +7302,9 @@
       <c r="I180" t="n">
         <v>12</v>
       </c>
+      <c r="J180" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6797,6 +7340,9 @@
       <c r="I181" t="n">
         <v>12</v>
       </c>
+      <c r="J181" t="n">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6832,6 +7378,9 @@
       <c r="I182" t="n">
         <v>12</v>
       </c>
+      <c r="J182" t="n">
+        <v>39.6</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6867,6 +7416,9 @@
       <c r="I183" t="n">
         <v>12</v>
       </c>
+      <c r="J183" t="n">
+        <v>39.4</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6902,6 +7454,9 @@
       <c r="I184" t="n">
         <v>12</v>
       </c>
+      <c r="J184" t="n">
+        <v>40.6</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6937,6 +7492,9 @@
       <c r="I185" t="n">
         <v>12</v>
       </c>
+      <c r="J185" t="n">
+        <v>40.5</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6972,6 +7530,9 @@
       <c r="I186" t="n">
         <v>12</v>
       </c>
+      <c r="J186" t="n">
+        <v>39.3</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7007,6 +7568,9 @@
       <c r="I187" t="n">
         <v>12</v>
       </c>
+      <c r="J187" t="n">
+        <v>39.7</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7042,6 +7606,9 @@
       <c r="I188" t="n">
         <v>12</v>
       </c>
+      <c r="J188" t="n">
+        <v>40.8</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7077,6 +7644,9 @@
       <c r="I189" t="n">
         <v>12</v>
       </c>
+      <c r="J189" t="n">
+        <v>40.1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7112,6 +7682,9 @@
       <c r="I190" t="n">
         <v>12</v>
       </c>
+      <c r="J190" t="n">
+        <v>39.2</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7147,6 +7720,9 @@
       <c r="I191" t="n">
         <v>12</v>
       </c>
+      <c r="J191" t="n">
+        <v>40.1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7182,6 +7758,9 @@
       <c r="I192" t="n">
         <v>12</v>
       </c>
+      <c r="J192" t="n">
+        <v>40.8</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7217,6 +7796,9 @@
       <c r="I193" t="n">
         <v>12</v>
       </c>
+      <c r="J193" t="n">
+        <v>39.7</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7252,6 +7834,9 @@
       <c r="I194" t="n">
         <v>12</v>
       </c>
+      <c r="J194" t="n">
+        <v>39.3</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7287,6 +7872,9 @@
       <c r="I195" t="n">
         <v>12</v>
       </c>
+      <c r="J195" t="n">
+        <v>40.5</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7322,6 +7910,9 @@
       <c r="I196" t="n">
         <v>12</v>
       </c>
+      <c r="J196" t="n">
+        <v>40.5</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7357,6 +7948,9 @@
       <c r="I197" t="n">
         <v>12</v>
       </c>
+      <c r="J197" t="n">
+        <v>39.4</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7392,6 +7986,9 @@
       <c r="I198" t="n">
         <v>12</v>
       </c>
+      <c r="J198" t="n">
+        <v>39.6</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7427,6 +8024,9 @@
       <c r="I199" t="n">
         <v>12</v>
       </c>
+      <c r="J199" t="n">
+        <v>40.7</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7462,6 +8062,9 @@
       <c r="I200" t="n">
         <v>12</v>
       </c>
+      <c r="J200" t="n">
+        <v>40.2</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7497,6 +8100,9 @@
       <c r="I201" t="n">
         <v>12</v>
       </c>
+      <c r="J201" t="n">
+        <v>39.2</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7532,6 +8138,9 @@
       <c r="I202" t="n">
         <v>12</v>
       </c>
+      <c r="J202" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7567,6 +8176,9 @@
       <c r="I203" t="n">
         <v>12</v>
       </c>
+      <c r="J203" t="n">
+        <v>40.8</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7602,6 +8214,9 @@
       <c r="I204" t="n">
         <v>12</v>
       </c>
+      <c r="J204" t="n">
+        <v>39.8</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7637,6 +8252,9 @@
       <c r="I205" t="n">
         <v>12</v>
       </c>
+      <c r="J205" t="n">
+        <v>39.3</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7672,6 +8290,9 @@
       <c r="I206" t="n">
         <v>12</v>
       </c>
+      <c r="J206" t="n">
+        <v>40.4</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7707,6 +8328,9 @@
       <c r="I207" t="n">
         <v>12</v>
       </c>
+      <c r="J207" t="n">
+        <v>40.6</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7742,6 +8366,9 @@
       <c r="I208" t="n">
         <v>12</v>
       </c>
+      <c r="J208" t="n">
+        <v>39.4</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7777,6 +8404,9 @@
       <c r="I209" t="n">
         <v>12</v>
       </c>
+      <c r="J209" t="n">
+        <v>39.5</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7812,6 +8442,9 @@
       <c r="I210" t="n">
         <v>12</v>
       </c>
+      <c r="J210" t="n">
+        <v>40.7</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7847,6 +8480,9 @@
       <c r="I211" t="n">
         <v>12</v>
       </c>
+      <c r="J211" t="n">
+        <v>40.3</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7882,6 +8518,9 @@
       <c r="I212" t="n">
         <v>12</v>
       </c>
+      <c r="J212" t="n">
+        <v>68.59999999999999</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7917,6 +8556,9 @@
       <c r="I213" t="n">
         <v>12</v>
       </c>
+      <c r="J213" t="n">
+        <v>70.2</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7952,6 +8594,9 @@
       <c r="I214" t="n">
         <v>12</v>
       </c>
+      <c r="J214" t="n">
+        <v>71.40000000000001</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7987,6 +8632,9 @@
       <c r="I215" t="n">
         <v>12</v>
       </c>
+      <c r="J215" t="n">
+        <v>69.5</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8022,6 +8670,9 @@
       <c r="I216" t="n">
         <v>12</v>
       </c>
+      <c r="J216" t="n">
+        <v>68.8</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8057,6 +8708,9 @@
       <c r="I217" t="n">
         <v>12</v>
       </c>
+      <c r="J217" t="n">
+        <v>70.8</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8092,6 +8746,9 @@
       <c r="I218" t="n">
         <v>12</v>
       </c>
+      <c r="J218" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8127,6 +8784,9 @@
       <c r="I219" t="n">
         <v>12</v>
       </c>
+      <c r="J219" t="n">
+        <v>68.90000000000001</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8162,6 +8822,9 @@
       <c r="I220" t="n">
         <v>12</v>
       </c>
+      <c r="J220" t="n">
+        <v>69.3</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8197,6 +8860,9 @@
       <c r="I221" t="n">
         <v>12</v>
       </c>
+      <c r="J221" t="n">
+        <v>71.3</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8232,6 +8898,9 @@
       <c r="I222" t="n">
         <v>12</v>
       </c>
+      <c r="J222" t="n">
+        <v>70.40000000000001</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8267,6 +8936,9 @@
       <c r="I223" t="n">
         <v>12</v>
       </c>
+      <c r="J223" t="n">
+        <v>68.59999999999999</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8302,6 +8974,9 @@
       <c r="I224" t="n">
         <v>12</v>
       </c>
+      <c r="J224" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8337,6 +9012,9 @@
       <c r="I225" t="n">
         <v>12</v>
       </c>
+      <c r="J225" t="n">
+        <v>71.40000000000001</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8372,6 +9050,9 @@
       <c r="I226" t="n">
         <v>12</v>
       </c>
+      <c r="J226" t="n">
+        <v>69.7</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8407,6 +9088,9 @@
       <c r="I227" t="n">
         <v>12</v>
       </c>
+      <c r="J227" t="n">
+        <v>68.7</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8442,6 +9126,9 @@
       <c r="I228" t="n">
         <v>12</v>
       </c>
+      <c r="J228" t="n">
+        <v>70.7</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8477,6 +9164,9 @@
       <c r="I229" t="n">
         <v>12</v>
       </c>
+      <c r="J229" t="n">
+        <v>71.09999999999999</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8512,6 +9202,9 @@
       <c r="I230" t="n">
         <v>12</v>
       </c>
+      <c r="J230" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8547,6 +9240,9 @@
       <c r="I231" t="n">
         <v>12</v>
       </c>
+      <c r="J231" t="n">
+        <v>69.09999999999999</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8582,6 +9278,9 @@
       <c r="I232" t="n">
         <v>12</v>
       </c>
+      <c r="J232" t="n">
+        <v>71.2</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8617,6 +9316,9 @@
       <c r="I233" t="n">
         <v>12</v>
       </c>
+      <c r="J233" t="n">
+        <v>70.59999999999999</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8652,6 +9354,9 @@
       <c r="I234" t="n">
         <v>12</v>
       </c>
+      <c r="J234" t="n">
+        <v>68.7</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8687,6 +9392,9 @@
       <c r="I235" t="n">
         <v>12</v>
       </c>
+      <c r="J235" t="n">
+        <v>69.8</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8722,6 +9430,9 @@
       <c r="I236" t="n">
         <v>12</v>
       </c>
+      <c r="J236" t="n">
+        <v>71.40000000000001</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8757,6 +9468,9 @@
       <c r="I237" t="n">
         <v>12</v>
       </c>
+      <c r="J237" t="n">
+        <v>69.90000000000001</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8792,6 +9506,9 @@
       <c r="I238" t="n">
         <v>12</v>
       </c>
+      <c r="J238" t="n">
+        <v>68.59999999999999</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8827,6 +9544,9 @@
       <c r="I239" t="n">
         <v>12</v>
       </c>
+      <c r="J239" t="n">
+        <v>70.5</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8862,6 +9582,9 @@
       <c r="I240" t="n">
         <v>12</v>
       </c>
+      <c r="J240" t="n">
+        <v>71.2</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8897,6 +9620,9 @@
       <c r="I241" t="n">
         <v>12</v>
       </c>
+      <c r="J241" t="n">
+        <v>69.2</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8932,6 +9658,9 @@
       <c r="I242" t="n">
         <v>12</v>
       </c>
+      <c r="J242" t="n">
+        <v>54.4</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8967,6 +9696,9 @@
       <c r="I243" t="n">
         <v>12</v>
       </c>
+      <c r="J243" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9002,6 +9734,9 @@
       <c r="I244" t="n">
         <v>12</v>
       </c>
+      <c r="J244" t="n">
+        <v>55.3</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9037,6 +9772,9 @@
       <c r="I245" t="n">
         <v>12</v>
       </c>
+      <c r="J245" t="n">
+        <v>53.9</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9072,6 +9810,9 @@
       <c r="I246" t="n">
         <v>12</v>
       </c>
+      <c r="J246" t="n">
+        <v>54.9</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9107,6 +9848,9 @@
       <c r="I247" t="n">
         <v>12</v>
       </c>
+      <c r="J247" t="n">
+        <v>56.1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9142,6 +9886,9 @@
       <c r="I248" t="n">
         <v>12</v>
       </c>
+      <c r="J248" t="n">
+        <v>54.8</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9177,6 +9924,9 @@
       <c r="I249" t="n">
         <v>12</v>
       </c>
+      <c r="J249" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9212,6 +9962,9 @@
       <c r="I250" t="n">
         <v>12</v>
       </c>
+      <c r="J250" t="n">
+        <v>55.5</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9247,6 +10000,9 @@
       <c r="I251" t="n">
         <v>12</v>
       </c>
+      <c r="J251" t="n">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9282,6 +10038,9 @@
       <c r="I252" t="n">
         <v>12</v>
       </c>
+      <c r="J252" t="n">
+        <v>54.3</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9317,6 +10076,9 @@
       <c r="I253" t="n">
         <v>12</v>
       </c>
+      <c r="J253" t="n">
+        <v>54.3</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9352,6 +10114,9 @@
       <c r="I254" t="n">
         <v>12</v>
       </c>
+      <c r="J254" t="n">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9387,6 +10152,9 @@
       <c r="I255" t="n">
         <v>12</v>
       </c>
+      <c r="J255" t="n">
+        <v>55.5</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9422,6 +10190,9 @@
       <c r="I256" t="n">
         <v>12</v>
       </c>
+      <c r="J256" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9457,6 +10228,9 @@
       <c r="I257" t="n">
         <v>12</v>
       </c>
+      <c r="J257" t="n">
+        <v>54.8</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9492,6 +10266,9 @@
       <c r="I258" t="n">
         <v>12</v>
       </c>
+      <c r="J258" t="n">
+        <v>56.1</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9527,6 +10304,9 @@
       <c r="I259" t="n">
         <v>12</v>
       </c>
+      <c r="J259" t="n">
+        <v>54.9</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9562,6 +10342,9 @@
       <c r="I260" t="n">
         <v>12</v>
       </c>
+      <c r="J260" t="n">
+        <v>53.9</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9597,6 +10380,9 @@
       <c r="I261" t="n">
         <v>12</v>
       </c>
+      <c r="J261" t="n">
+        <v>55.3</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9632,6 +10418,9 @@
       <c r="I262" t="n">
         <v>12</v>
       </c>
+      <c r="J262" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9667,6 +10456,9 @@
       <c r="I263" t="n">
         <v>12</v>
       </c>
+      <c r="J263" t="n">
+        <v>54.4</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9702,6 +10494,9 @@
       <c r="I264" t="n">
         <v>12</v>
       </c>
+      <c r="J264" t="n">
+        <v>54.2</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9737,6 +10532,9 @@
       <c r="I265" t="n">
         <v>12</v>
       </c>
+      <c r="J265" t="n">
+        <v>55.8</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9772,6 +10570,9 @@
       <c r="I266" t="n">
         <v>12</v>
       </c>
+      <c r="J266" t="n">
+        <v>55.6</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9807,6 +10608,9 @@
       <c r="I267" t="n">
         <v>12</v>
       </c>
+      <c r="J267" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9842,6 +10646,9 @@
       <c r="I268" t="n">
         <v>12</v>
       </c>
+      <c r="J268" t="n">
+        <v>54.6</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9877,6 +10684,9 @@
       <c r="I269" t="n">
         <v>12</v>
       </c>
+      <c r="J269" t="n">
+        <v>56.1</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9912,6 +10722,9 @@
       <c r="I270" t="n">
         <v>12</v>
       </c>
+      <c r="J270" t="n">
+        <v>55.1</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9947,6 +10760,9 @@
       <c r="I271" t="n">
         <v>12</v>
       </c>
+      <c r="J271" t="n">
+        <v>53.9</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9982,6 +10798,9 @@
       <c r="I272" t="n">
         <v>12</v>
       </c>
+      <c r="J272" t="n">
+        <v>95.8</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10017,6 +10836,9 @@
       <c r="I273" t="n">
         <v>12</v>
       </c>
+      <c r="J273" t="n">
+        <v>96.59999999999999</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10052,6 +10874,9 @@
       <c r="I274" t="n">
         <v>12</v>
       </c>
+      <c r="J274" t="n">
+        <v>93.8</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10087,6 +10912,9 @@
       <c r="I275" t="n">
         <v>12</v>
       </c>
+      <c r="J275" t="n">
+        <v>93.7</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10122,6 +10950,9 @@
       <c r="I276" t="n">
         <v>12</v>
       </c>
+      <c r="J276" t="n">
+        <v>96.5</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10157,6 +10988,9 @@
       <c r="I277" t="n">
         <v>12</v>
       </c>
+      <c r="J277" t="n">
+        <v>95.90000000000001</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10192,6 +11026,9 @@
       <c r="I278" t="n">
         <v>12</v>
       </c>
+      <c r="J278" t="n">
+        <v>93.2</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10227,6 +11064,9 @@
       <c r="I279" t="n">
         <v>12</v>
       </c>
+      <c r="J279" t="n">
+        <v>94.59999999999999</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10262,6 +11102,9 @@
       <c r="I280" t="n">
         <v>12</v>
       </c>
+      <c r="J280" t="n">
+        <v>96.90000000000001</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10297,6 +11140,9 @@
       <c r="I281" t="n">
         <v>12</v>
       </c>
+      <c r="J281" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10332,6 +11178,9 @@
       <c r="I282" t="n">
         <v>12</v>
       </c>
+      <c r="J282" t="n">
+        <v>93.09999999999999</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10367,6 +11216,9 @@
       <c r="I283" t="n">
         <v>12</v>
       </c>
+      <c r="J283" t="n">
+        <v>95.5</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10402,6 +11254,9 @@
       <c r="I284" t="n">
         <v>12</v>
       </c>
+      <c r="J284" t="n">
+        <v>96.7</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10437,6 +11292,9 @@
       <c r="I285" t="n">
         <v>12</v>
       </c>
+      <c r="J285" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10472,6 +11330,9 @@
       <c r="I286" t="n">
         <v>12</v>
       </c>
+      <c r="J286" t="n">
+        <v>93.5</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10507,6 +11368,9 @@
       <c r="I287" t="n">
         <v>12</v>
       </c>
+      <c r="J287" t="n">
+        <v>96.40000000000001</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10542,6 +11406,9 @@
       <c r="I288" t="n">
         <v>12</v>
       </c>
+      <c r="J288" t="n">
+        <v>96.09999999999999</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10577,6 +11444,9 @@
       <c r="I289" t="n">
         <v>12</v>
       </c>
+      <c r="J289" t="n">
+        <v>93.3</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10612,6 +11482,9 @@
       <c r="I290" t="n">
         <v>12</v>
       </c>
+      <c r="J290" t="n">
+        <v>94.3</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10647,6 +11520,9 @@
       <c r="I291" t="n">
         <v>12</v>
       </c>
+      <c r="J291" t="n">
+        <v>96.8</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10682,6 +11558,9 @@
       <c r="I292" t="n">
         <v>12</v>
       </c>
+      <c r="J292" t="n">
+        <v>95.2</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10717,6 +11596,9 @@
       <c r="I293" t="n">
         <v>12</v>
       </c>
+      <c r="J293" t="n">
+        <v>93.09999999999999</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10752,6 +11634,9 @@
       <c r="I294" t="n">
         <v>12</v>
       </c>
+      <c r="J294" t="n">
+        <v>95.3</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10787,6 +11672,9 @@
       <c r="I295" t="n">
         <v>12</v>
       </c>
+      <c r="J295" t="n">
+        <v>96.8</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10822,6 +11710,9 @@
       <c r="I296" t="n">
         <v>12</v>
       </c>
+      <c r="J296" t="n">
+        <v>94.3</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10857,6 +11748,9 @@
       <c r="I297" t="n">
         <v>12</v>
       </c>
+      <c r="J297" t="n">
+        <v>93.40000000000001</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10892,6 +11786,9 @@
       <c r="I298" t="n">
         <v>12</v>
       </c>
+      <c r="J298" t="n">
+        <v>96.2</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10927,6 +11824,9 @@
       <c r="I299" t="n">
         <v>12</v>
       </c>
+      <c r="J299" t="n">
+        <v>96.40000000000001</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10962,6 +11862,9 @@
       <c r="I300" t="n">
         <v>12</v>
       </c>
+      <c r="J300" t="n">
+        <v>93.5</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10997,6 +11900,9 @@
       <c r="I301" t="n">
         <v>12</v>
       </c>
+      <c r="J301" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11032,6 +11938,9 @@
       <c r="I302" t="n">
         <v>12</v>
       </c>
+      <c r="J302" t="n">
+        <v>30.6</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11067,6 +11976,9 @@
       <c r="I303" t="n">
         <v>12</v>
       </c>
+      <c r="J303" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11102,6 +12014,9 @@
       <c r="I304" t="n">
         <v>12</v>
       </c>
+      <c r="J304" t="n">
+        <v>29.4</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11137,6 +12052,9 @@
       <c r="I305" t="n">
         <v>12</v>
       </c>
+      <c r="J305" t="n">
+        <v>30.1</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11172,6 +12090,9 @@
       <c r="I306" t="n">
         <v>12</v>
       </c>
+      <c r="J306" t="n">
+        <v>30.6</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11207,6 +12128,9 @@
       <c r="I307" t="n">
         <v>12</v>
       </c>
+      <c r="J307" t="n">
+        <v>29.7</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11242,6 +12166,9 @@
       <c r="I308" t="n">
         <v>12</v>
       </c>
+      <c r="J308" t="n">
+        <v>29.5</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11277,6 +12204,9 @@
       <c r="I309" t="n">
         <v>12</v>
       </c>
+      <c r="J309" t="n">
+        <v>30.4</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11312,6 +12242,9 @@
       <c r="I310" t="n">
         <v>12</v>
       </c>
+      <c r="J310" t="n">
+        <v>30.4</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11347,6 +12280,9 @@
       <c r="I311" t="n">
         <v>12</v>
       </c>
+      <c r="J311" t="n">
+        <v>29.5</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11382,6 +12318,9 @@
       <c r="I312" t="n">
         <v>12</v>
       </c>
+      <c r="J312" t="n">
+        <v>29.8</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11417,6 +12356,9 @@
       <c r="I313" t="n">
         <v>12</v>
       </c>
+      <c r="J313" t="n">
+        <v>30.6</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11452,6 +12394,9 @@
       <c r="I314" t="n">
         <v>12</v>
       </c>
+      <c r="J314" t="n">
+        <v>30.1</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11487,6 +12432,9 @@
       <c r="I315" t="n">
         <v>12</v>
       </c>
+      <c r="J315" t="n">
+        <v>29.4</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11522,6 +12470,9 @@
       <c r="I316" t="n">
         <v>12</v>
       </c>
+      <c r="J316" t="n">
+        <v>30.1</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11557,6 +12508,9 @@
       <c r="I317" t="n">
         <v>12</v>
       </c>
+      <c r="J317" t="n">
+        <v>30.6</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11592,6 +12546,9 @@
       <c r="I318" t="n">
         <v>12</v>
       </c>
+      <c r="J318" t="n">
+        <v>29.8</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11627,6 +12584,9 @@
       <c r="I319" t="n">
         <v>12</v>
       </c>
+      <c r="J319" t="n">
+        <v>29.5</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11662,6 +12622,9 @@
       <c r="I320" t="n">
         <v>12</v>
       </c>
+      <c r="J320" t="n">
+        <v>30.3</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11697,6 +12660,9 @@
       <c r="I321" t="n">
         <v>12</v>
       </c>
+      <c r="J321" t="n">
+        <v>30.4</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11732,6 +12698,9 @@
       <c r="I322" t="n">
         <v>12</v>
       </c>
+      <c r="J322" t="n">
+        <v>29.5</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11767,6 +12736,9 @@
       <c r="I323" t="n">
         <v>12</v>
       </c>
+      <c r="J323" t="n">
+        <v>29.7</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11802,6 +12774,9 @@
       <c r="I324" t="n">
         <v>12</v>
       </c>
+      <c r="J324" t="n">
+        <v>30.5</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11837,6 +12812,9 @@
       <c r="I325" t="n">
         <v>12</v>
       </c>
+      <c r="J325" t="n">
+        <v>30.2</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11872,6 +12850,9 @@
       <c r="I326" t="n">
         <v>12</v>
       </c>
+      <c r="J326" t="n">
+        <v>29.4</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11907,6 +12888,9 @@
       <c r="I327" t="n">
         <v>12</v>
       </c>
+      <c r="J327" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11942,6 +12926,9 @@
       <c r="I328" t="n">
         <v>12</v>
       </c>
+      <c r="J328" t="n">
+        <v>30.6</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11977,6 +12964,9 @@
       <c r="I329" t="n">
         <v>12</v>
       </c>
+      <c r="J329" t="n">
+        <v>29.9</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12012,6 +13002,9 @@
       <c r="I330" t="n">
         <v>12</v>
       </c>
+      <c r="J330" t="n">
+        <v>29.4</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12047,6 +13040,9 @@
       <c r="I331" t="n">
         <v>12</v>
       </c>
+      <c r="J331" t="n">
+        <v>30.3</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12082,6 +13078,9 @@
       <c r="I332" t="n">
         <v>12</v>
       </c>
+      <c r="J332" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12117,6 +13116,9 @@
       <c r="I333" t="n">
         <v>12</v>
       </c>
+      <c r="J333" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12152,6 +13154,9 @@
       <c r="I334" t="n">
         <v>12</v>
       </c>
+      <c r="J334" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12187,6 +13192,9 @@
       <c r="I335" t="n">
         <v>12</v>
       </c>
+      <c r="J335" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12222,6 +13230,9 @@
       <c r="I336" t="n">
         <v>12</v>
       </c>
+      <c r="J336" t="n">
+        <v>22.1</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12257,6 +13268,9 @@
       <c r="I337" t="n">
         <v>12</v>
       </c>
+      <c r="J337" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -12292,6 +13306,9 @@
       <c r="I338" t="n">
         <v>12</v>
       </c>
+      <c r="J338" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12327,6 +13344,9 @@
       <c r="I339" t="n">
         <v>12</v>
       </c>
+      <c r="J339" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12362,6 +13382,9 @@
       <c r="I340" t="n">
         <v>12</v>
       </c>
+      <c r="J340" t="n">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12397,6 +13420,9 @@
       <c r="I341" t="n">
         <v>12</v>
       </c>
+      <c r="J341" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12432,6 +13458,9 @@
       <c r="I342" t="n">
         <v>12</v>
       </c>
+      <c r="J342" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12467,6 +13496,9 @@
       <c r="I343" t="n">
         <v>12</v>
       </c>
+      <c r="J343" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12502,6 +13534,9 @@
       <c r="I344" t="n">
         <v>12</v>
       </c>
+      <c r="J344" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12537,6 +13572,9 @@
       <c r="I345" t="n">
         <v>12</v>
       </c>
+      <c r="J345" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12572,6 +13610,9 @@
       <c r="I346" t="n">
         <v>12</v>
       </c>
+      <c r="J346" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12607,6 +13648,9 @@
       <c r="I347" t="n">
         <v>12</v>
       </c>
+      <c r="J347" t="n">
+        <v>22.1</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12642,6 +13686,9 @@
       <c r="I348" t="n">
         <v>12</v>
       </c>
+      <c r="J348" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12677,6 +13724,9 @@
       <c r="I349" t="n">
         <v>12</v>
       </c>
+      <c r="J349" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12712,6 +13762,9 @@
       <c r="I350" t="n">
         <v>12</v>
       </c>
+      <c r="J350" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12747,6 +13800,9 @@
       <c r="I351" t="n">
         <v>12</v>
       </c>
+      <c r="J351" t="n">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -12782,6 +13838,9 @@
       <c r="I352" t="n">
         <v>12</v>
       </c>
+      <c r="J352" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12817,6 +13876,9 @@
       <c r="I353" t="n">
         <v>12</v>
       </c>
+      <c r="J353" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12852,6 +13914,9 @@
       <c r="I354" t="n">
         <v>12</v>
       </c>
+      <c r="J354" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12887,6 +13952,9 @@
       <c r="I355" t="n">
         <v>12</v>
       </c>
+      <c r="J355" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12922,6 +13990,9 @@
       <c r="I356" t="n">
         <v>12</v>
       </c>
+      <c r="J356" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12957,6 +14028,9 @@
       <c r="I357" t="n">
         <v>12</v>
       </c>
+      <c r="J357" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12992,6 +14066,9 @@
       <c r="I358" t="n">
         <v>12</v>
       </c>
+      <c r="J358" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13027,6 +14104,9 @@
       <c r="I359" t="n">
         <v>12</v>
       </c>
+      <c r="J359" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13062,6 +14142,9 @@
       <c r="I360" t="n">
         <v>12</v>
       </c>
+      <c r="J360" t="n">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -13097,6 +14180,9 @@
       <c r="I361" t="n">
         <v>12</v>
       </c>
+      <c r="J361" t="n">
+        <v>22.4</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -13132,6 +14218,9 @@
       <c r="I362" t="n">
         <v>12</v>
       </c>
+      <c r="J362" t="n">
+        <v>49.7</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -13167,6 +14256,9 @@
       <c r="I363" t="n">
         <v>12</v>
       </c>
+      <c r="J363" t="n">
+        <v>49.1</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -13202,6 +14294,9 @@
       <c r="I364" t="n">
         <v>12</v>
       </c>
+      <c r="J364" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -13237,6 +14332,9 @@
       <c r="I365" t="n">
         <v>12</v>
       </c>
+      <c r="J365" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -13272,6 +14370,9 @@
       <c r="I366" t="n">
         <v>12</v>
       </c>
+      <c r="J366" t="n">
+        <v>65.8</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -13307,6 +14408,9 @@
       <c r="I367" t="n">
         <v>12</v>
       </c>
+      <c r="J367" t="n">
+        <v>67.3</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -13342,6 +14446,9 @@
       <c r="I368" t="n">
         <v>12</v>
       </c>
+      <c r="J368" t="n">
+        <v>65.90000000000001</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13377,6 +14484,9 @@
       <c r="I369" t="n">
         <v>12</v>
       </c>
+      <c r="J369" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13412,6 +14522,9 @@
       <c r="I370" t="n">
         <v>12</v>
       </c>
+      <c r="J370" t="n">
+        <v>66.5</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13447,6 +14560,9 @@
       <c r="I371" t="n">
         <v>12</v>
       </c>
+      <c r="J371" t="n">
+        <v>67.2</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13482,6 +14598,9 @@
       <c r="I372" t="n">
         <v>12</v>
       </c>
+      <c r="J372" t="n">
+        <v>65.2</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -13517,6 +14636,9 @@
       <c r="I373" t="n">
         <v>12</v>
       </c>
+      <c r="J373" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13552,6 +14674,9 @@
       <c r="I374" t="n">
         <v>12</v>
       </c>
+      <c r="J374" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13587,6 +14712,9 @@
       <c r="I375" t="n">
         <v>12</v>
       </c>
+      <c r="J375" t="n">
+        <v>66.7</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13622,6 +14750,9 @@
       <c r="I376" t="n">
         <v>12</v>
       </c>
+      <c r="J376" t="n">
+        <v>64.8</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13657,6 +14788,9 @@
       <c r="I377" t="n">
         <v>12</v>
       </c>
+      <c r="J377" t="n">
+        <v>65.59999999999999</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13692,6 +14826,9 @@
       <c r="I378" t="n">
         <v>12</v>
       </c>
+      <c r="J378" t="n">
+        <v>67.3</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13727,6 +14864,9 @@
       <c r="I379" t="n">
         <v>12</v>
       </c>
+      <c r="J379" t="n">
+        <v>66.09999999999999</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13762,6 +14902,9 @@
       <c r="I380" t="n">
         <v>12</v>
       </c>
+      <c r="J380" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13797,6 +14940,9 @@
       <c r="I381" t="n">
         <v>12</v>
       </c>
+      <c r="J381" t="n">
+        <v>66.3</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13832,6 +14978,9 @@
       <c r="I382" t="n">
         <v>12</v>
       </c>
+      <c r="J382" t="n">
+        <v>67.2</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13867,6 +15016,9 @@
       <c r="I383" t="n">
         <v>12</v>
       </c>
+      <c r="J383" t="n">
+        <v>65.40000000000001</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13902,6 +15054,9 @@
       <c r="I384" t="n">
         <v>12</v>
       </c>
+      <c r="J384" t="n">
+        <v>64.90000000000001</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -13937,6 +15092,9 @@
       <c r="I385" t="n">
         <v>12</v>
       </c>
+      <c r="J385" t="n">
+        <v>66.90000000000001</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13972,6 +15130,9 @@
       <c r="I386" t="n">
         <v>12</v>
       </c>
+      <c r="J386" t="n">
+        <v>66.90000000000001</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -14007,6 +15168,9 @@
       <c r="I387" t="n">
         <v>12</v>
       </c>
+      <c r="J387" t="n">
+        <v>64.90000000000001</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -14042,6 +15206,9 @@
       <c r="I388" t="n">
         <v>12</v>
       </c>
+      <c r="J388" t="n">
+        <v>65.40000000000001</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -14077,6 +15244,9 @@
       <c r="I389" t="n">
         <v>12</v>
       </c>
+      <c r="J389" t="n">
+        <v>67.3</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -14112,6 +15282,9 @@
       <c r="I390" t="n">
         <v>12</v>
       </c>
+      <c r="J390" t="n">
+        <v>66.2</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -14147,6 +15320,9 @@
       <c r="I391" t="n">
         <v>12</v>
       </c>
+      <c r="J391" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -14182,6 +15358,9 @@
       <c r="I392" t="n">
         <v>12</v>
       </c>
+      <c r="J392" t="n">
+        <v>66.09999999999999</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -14217,6 +15396,9 @@
       <c r="I393" t="n">
         <v>12</v>
       </c>
+      <c r="J393" t="n">
+        <v>67.3</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -14251,6 +15433,9 @@
       </c>
       <c r="I394" t="n">
         <v>12</v>
+      </c>
+      <c r="J394" t="n">
+        <v>65.59999999999999</v>
       </c>
     </row>
   </sheetData>
